--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-28).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-28).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 3.024,24</t>
-  </si>
-  <si>
-    <t>34.3</t>
-  </si>
-  <si>
-    <t>21.4</t>
-  </si>
-  <si>
-    <t>4.61</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 3.006,75</t>
+  </si>
+  <si>
+    <t>34.1</t>
+  </si>
+  <si>
+    <t>21.2</t>
+  </si>
+  <si>
+    <t>4.62</t>
   </si>
   <si>
     <t>17.8</t>
@@ -956,13 +956,13 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>45.3%</t>
-  </si>
-  <si>
-    <t>17.3%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>45.2%</t>
+  </si>
+  <si>
+    <t>17.1%</t>
   </si>
   <si>
     <t>1.8%</t>
@@ -977,7 +977,7 @@
     <t>1.5%</t>
   </si>
   <si>
-    <t>6.8%</t>
+    <t>6.7%</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -986,10 +986,10 @@
     <t>3.8%</t>
   </si>
   <si>
-    <t>819.0</t>
-  </si>
-  <si>
-    <t>657.0</t>
+    <t>827.0</t>
+  </si>
+  <si>
+    <t>664.0</t>
   </si>
   <si>
     <t>70.0</t>
@@ -998,22 +998,22 @@
     <t>9.0</t>
   </si>
   <si>
-    <t>172.0</t>
-  </si>
-  <si>
-    <t>57.0</t>
+    <t>173.0</t>
+  </si>
+  <si>
+    <t>58.0</t>
   </si>
   <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>258.0</t>
-  </si>
-  <si>
-    <t>94.0</t>
-  </si>
-  <si>
-    <t>144.0</t>
+    <t>260.0</t>
+  </si>
+  <si>
+    <t>96.0</t>
+  </si>
+  <si>
+    <t>146.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -6782,7 +6782,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6812,35 +6812,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>4667.3800000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>38</v>
+      </c>
+      <c r="O36" s="6">
+        <v>27</v>
+      </c>
+      <c r="P36" s="7">
+        <v>5.2092583333333335</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>16.489742307692307</v>
+      </c>
+      <c r="R36" s="8">
+        <v>4.3871807692307687</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.42307692307692307</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7664,7 +7722,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7694,35 +7752,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>2082.0900000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>29</v>
+      </c>
+      <c r="O42" s="6">
+        <v>21</v>
+      </c>
+      <c r="P42" s="7">
+        <v>4.5047607142857142</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>17.159523809523812</v>
+      </c>
+      <c r="R42" s="8">
+        <v>5.5214285714285714</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9013,7 +9129,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9043,35 +9159,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>481.69999999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>4</v>
+      </c>
+      <c r="O51" s="6">
+        <v>1</v>
+      </c>
+      <c r="P51" s="7">
+        <v>5.6458250000000003</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>24.916699999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>6.1666999999999996</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -10082,33 +10256,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>19</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -16516,7 +16736,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16546,35 +16766,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>1815.3</v>
+      </c>
+      <c r="N102" s="6">
+        <v>23</v>
+      </c>
+      <c r="O102" s="6">
+        <v>17</v>
+      </c>
+      <c r="P102" s="7">
+        <v>4.8007590909090903</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>17.290194117647058</v>
+      </c>
+      <c r="R102" s="8">
+        <v>6.1270812499999998</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -30271,7 +30549,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30301,14 +30579,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>2856.9299999999998</v>
+      </c>
+      <c r="N195" s="6">
+        <v>37</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>4.0779411764705884</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>15.332405555555555</v>
+      </c>
+      <c r="R195" s="8">
+        <v>4.2666666666666666</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
